--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N54_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N54_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>5.903491903999919</v>
       </c>
       <c r="E2" t="n">
-        <v>3.951403868347886</v>
+        <v>3.904720579470474</v>
       </c>
       <c r="F2" t="n">
-        <v>1.68579679685487</v>
+        <v>1.691031218950107</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>2.531898310290178</v>
       </c>
       <c r="E3" t="n">
-        <v>3.951403868347886</v>
+        <v>3.904720579470474</v>
       </c>
       <c r="F3" t="n">
-        <v>1.68579679685487</v>
+        <v>1.691031218950107</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -529,6 +529,38 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W0029F0003T0006Z000C1N54.png</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.420327549533337</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.133850798006515</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.904720579470474</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.691031218950107</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>T7604</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N54_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N54_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.03756628684596</v>
+        <v>1.631104521612468</v>
       </c>
       <c r="D2" t="n">
-        <v>5.903491903999919</v>
+        <v>0.9593174343999868</v>
       </c>
       <c r="E2" t="n">
-        <v>3.904720579470474</v>
+        <v>0.6345170941639521</v>
       </c>
       <c r="F2" t="n">
-        <v>1.691031218950107</v>
+        <v>0.2747925730793923</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2.134758550150185</v>
+        <v>0.3468982643994051</v>
       </c>
       <c r="D3" t="n">
-        <v>2.531898310290178</v>
+        <v>0.411433475422154</v>
       </c>
       <c r="E3" t="n">
-        <v>3.904720579470474</v>
+        <v>0.6345170941639521</v>
       </c>
       <c r="F3" t="n">
-        <v>1.691031218950107</v>
+        <v>0.2747925730793923</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>1.420327549533337</v>
+        <v>0.2308032267991672</v>
       </c>
       <c r="D4" t="n">
-        <v>2.133850798006515</v>
+        <v>0.3467507546760588</v>
       </c>
       <c r="E4" t="n">
-        <v>3.904720579470474</v>
+        <v>0.6345170941639521</v>
       </c>
       <c r="F4" t="n">
-        <v>1.691031218950107</v>
+        <v>0.2747925730793923</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
